--- a/src/test/resources/testdata/Modules/13_DreamGift/DreamGift/01_DreamGiftTest.xlsx
+++ b/src/test/resources/testdata/Modules/13_DreamGift/DreamGift/01_DreamGiftTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\13_DreamGift\DreamGift\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9787808-7AC8-4234-8EE8-952BEC851AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BCE7E2-D6EC-4D0A-8B2B-BABA37C2705A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -851,11 +851,12 @@
 Indoor Games</t>
   </si>
   <si>
+    <t>verify_giftcodeinlist</t>
+  </si>
+  <si>
     <t>clickon_alertdialog_yesbtn
-verify_nodataavailable_text</t>
-  </si>
-  <si>
-    <t>verify_giftcodeinlist</t>
+verify_nodataavailable_text
+navigatebacktodashboardpage</t>
   </si>
 </sst>
 </file>
@@ -2103,7 +2104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
@@ -2153,7 +2154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
@@ -2167,7 +2168,7 @@
         <v>39</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
